--- a/reports/Debug-purgatory-20260105/For Winter Ending (Prior Year)_Payroll_history.xlsx
+++ b/reports/Debug-purgatory-20260105/For Winter Ending (Prior Year)_Payroll_history.xlsx
@@ -22,6 +22,21 @@
     <t>D6215</t>
   </si>
   <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D1501</t>
+  </si>
+  <si>
+    <t>D5203</t>
+  </si>
+  <si>
+    <t>D5810</t>
+  </si>
+  <si>
     <t>D5820</t>
   </si>
   <si>
@@ -44,21 +59,6 @@
   </si>
   <si>
     <t>D8810</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D1501</t>
-  </si>
-  <si>
-    <t>D5203</t>
-  </si>
-  <si>
-    <t>D5810</t>
   </si>
   <si>
     <t>D2200</t>
@@ -548,7 +548,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>38181.66</v>
+        <v>97287.33</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -556,7 +556,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>114482.74</v>
+        <v>63171.85</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -564,7 +564,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>12930.90</v>
+        <v>1557.58</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -572,7 +572,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>248558.38</v>
+        <v>1777.14</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -580,7 +580,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>57411.01</v>
+        <v>13129.38</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -588,7 +588,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>12906.89</v>
+        <v>38181.66</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -596,7 +596,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>23360.65</v>
+        <v>114482.74</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -604,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>228.24</v>
+        <v>12930.90</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -612,7 +612,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>97287.33</v>
+        <v>248558.38</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -620,7 +620,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>63171.85</v>
+        <v>57411.01</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -628,7 +628,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>1557.58</v>
+        <v>12906.89</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -636,7 +636,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>1777.14</v>
+        <v>23360.65</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -644,7 +644,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>13129.38</v>
+        <v>228.24</v>
       </c>
     </row>
     <row r="16" spans="1:2">
